--- a/site/일일근태.xlsx
+++ b/site/일일근태.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김남훈\Desktop\site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A8C430-C9CF-4232-A4B3-BC610A57D0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364DE470-F075-4640-A031-39CC96F08865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E82BFD2-9AED-4833-B309-E05E41D5A9F7}"/>
   </bookViews>
@@ -385,8 +385,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy/mm/dd\(aaa\)"/>
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd\(aaa\)"/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -520,7 +520,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -550,36 +550,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -878,7 +848,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -897,122 +867,116 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="13" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="13" fillId="3" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="13" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="13" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1301,6 +1265,7 @@
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
     <col min="2" max="2" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1403,29 +1368,29 @@
     </row>
     <row r="4" spans="1:29" ht="16.5" customHeight="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="38"/>
-      <c r="F4" s="33" t="s">
+      <c r="E4" s="42"/>
+      <c r="F4" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="33" t="s">
+      <c r="I4" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="J4" s="36" t="s">
         <v>18</v>
       </c>
       <c r="K4" s="7" t="s">
@@ -1434,61 +1399,61 @@
       <c r="L4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="33" t="s">
+      <c r="M4" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="O4" s="33" t="s">
+      <c r="O4" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="39" t="s">
+      <c r="P4" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="39" t="s">
+      <c r="Q4" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="R4" s="40" t="s">
+      <c r="R4" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="S4" s="39" t="s">
+      <c r="S4" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="T4" s="39" t="s">
+      <c r="T4" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="U4" s="33" t="s">
+      <c r="U4" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="V4" s="39" t="s">
+      <c r="V4" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="W4" s="39" t="s">
+      <c r="W4" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="X4" s="39" t="s">
+      <c r="X4" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="Y4" s="44" t="s">
+      <c r="Y4" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="Z4" s="39" t="s">
+      <c r="Z4" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="AA4" s="39" t="s">
+      <c r="AA4" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="AB4" s="39" t="s">
+      <c r="AB4" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="AC4" s="42" t="s">
+      <c r="AC4" s="31" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:29">
       <c r="A5" s="3"/>
-      <c r="B5" s="36"/>
+      <c r="B5" s="40"/>
       <c r="C5" s="34"/>
       <c r="D5" s="8" t="s">
         <v>37</v>
@@ -1512,7 +1477,7 @@
       <c r="O5" s="34"/>
       <c r="P5" s="34"/>
       <c r="Q5" s="34"/>
-      <c r="R5" s="41"/>
+      <c r="R5" s="38"/>
       <c r="S5" s="34"/>
       <c r="T5" s="34"/>
       <c r="U5" s="34"/>
@@ -1523,7 +1488,7 @@
       <c r="Z5" s="34"/>
       <c r="AA5" s="34"/>
       <c r="AB5" s="34"/>
-      <c r="AC5" s="43"/>
+      <c r="AC5" s="32"/>
     </row>
     <row r="6" spans="1:29" ht="17.25" thickBot="1">
       <c r="A6" s="9"/>
@@ -1540,1126 +1505,1126 @@
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="12">
-        <f t="shared" ref="I6:AC6" si="0">+COUNTIF(I7:I26,"O")</f>
+        <f>+COUNTIF(I7:I200,"O")</f>
         <v>0</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
+        <f t="shared" ref="J6:AC6" si="0">+COUNTIF(J7:J200,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K6" s="13">
+      <c r="L6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L6" s="13">
+      <c r="M6" s="12">
+        <f>+COUNTIF(M7:M200,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M6" s="13">
+      <c r="O6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N6" s="13">
+      <c r="P6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O6" s="13">
+      <c r="Q6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P6" s="13">
+      <c r="R6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="S6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R6" s="13">
+      <c r="T6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S6" s="13">
+      <c r="U6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T6" s="13">
+      <c r="V6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U6" s="13">
+      <c r="W6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V6" s="13">
+      <c r="X6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W6" s="13">
+      <c r="Y6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X6" s="13">
+      <c r="Z6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y6" s="13">
+      <c r="AA6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z6" s="13">
+      <c r="AB6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA6" s="13">
+      <c r="AC6" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB6" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC6" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="7" spans="1:29">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16" cm="1">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14" cm="1">
         <f t="array" ref="B7:B91">IF(C7:C91&lt;&gt;"",ROW(C7:C91)-6,"")</f>
         <v>1</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="I7" s="19"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
-      <c r="T7" s="21"/>
-      <c r="U7" s="21"/>
-      <c r="V7" s="21"/>
-      <c r="W7" s="21"/>
-      <c r="X7" s="21"/>
-      <c r="Y7" s="21"/>
-      <c r="Z7" s="21"/>
-      <c r="AA7" s="21"/>
-      <c r="AB7" s="21"/>
-      <c r="AC7" s="22"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="19"/>
+      <c r="AA7" s="19"/>
+      <c r="AB7" s="19"/>
+      <c r="AC7" s="20"/>
     </row>
     <row r="8" spans="1:29">
-      <c r="A8" s="15"/>
-      <c r="B8" s="17">
+      <c r="A8" s="13"/>
+      <c r="B8" s="15">
         <v>2</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="23"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="23"/>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="23"/>
-      <c r="AC8" s="26"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+      <c r="V8" s="21"/>
+      <c r="W8" s="21"/>
+      <c r="X8" s="21"/>
+      <c r="Y8" s="21"/>
+      <c r="Z8" s="21"/>
+      <c r="AA8" s="21"/>
+      <c r="AB8" s="21"/>
+      <c r="AC8" s="24"/>
     </row>
     <row r="9" spans="1:29">
-      <c r="A9" s="15"/>
-      <c r="B9" s="17">
+      <c r="A9" s="13"/>
+      <c r="B9" s="15">
         <v>3</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="G9" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I9" s="23"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="23"/>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="23"/>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="23"/>
-      <c r="AC9" s="26"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="21"/>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="21"/>
+      <c r="AA9" s="21"/>
+      <c r="AB9" s="21"/>
+      <c r="AC9" s="24"/>
     </row>
     <row r="10" spans="1:29">
-      <c r="A10" s="15"/>
-      <c r="B10" s="17">
+      <c r="A10" s="13"/>
+      <c r="B10" s="15">
         <v>4</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G10" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I10" s="23"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="23"/>
-      <c r="W10" s="23"/>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="23"/>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="23"/>
-      <c r="AC10" s="26"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="21"/>
+      <c r="V10" s="21"/>
+      <c r="W10" s="21"/>
+      <c r="X10" s="21"/>
+      <c r="Y10" s="21"/>
+      <c r="Z10" s="21"/>
+      <c r="AA10" s="21"/>
+      <c r="AB10" s="21"/>
+      <c r="AC10" s="24"/>
     </row>
     <row r="11" spans="1:29">
-      <c r="A11" s="15"/>
-      <c r="B11" s="17">
+      <c r="A11" s="13"/>
+      <c r="B11" s="15">
         <v>5</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="23" t="s">
+      <c r="H11" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I11" s="23"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="23"/>
-      <c r="X11" s="23"/>
-      <c r="Y11" s="23"/>
-      <c r="Z11" s="23"/>
-      <c r="AA11" s="23"/>
-      <c r="AB11" s="23"/>
-      <c r="AC11" s="26"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="21"/>
+      <c r="V11" s="21"/>
+      <c r="W11" s="21"/>
+      <c r="X11" s="21"/>
+      <c r="Y11" s="21"/>
+      <c r="Z11" s="21"/>
+      <c r="AA11" s="21"/>
+      <c r="AB11" s="21"/>
+      <c r="AC11" s="24"/>
     </row>
     <row r="12" spans="1:29">
-      <c r="A12" s="15"/>
-      <c r="B12" s="17">
+      <c r="A12" s="13"/>
+      <c r="B12" s="15">
         <v>6</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="H12" s="23" t="s">
+      <c r="H12" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I12" s="23"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="23"/>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="23"/>
-      <c r="AA12" s="23"/>
-      <c r="AB12" s="23"/>
-      <c r="AC12" s="26"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="21"/>
+      <c r="W12" s="21"/>
+      <c r="X12" s="21"/>
+      <c r="Y12" s="21"/>
+      <c r="Z12" s="21"/>
+      <c r="AA12" s="21"/>
+      <c r="AB12" s="21"/>
+      <c r="AC12" s="24"/>
     </row>
     <row r="13" spans="1:29">
-      <c r="A13" s="15"/>
-      <c r="B13" s="17">
+      <c r="A13" s="13"/>
+      <c r="B13" s="15">
         <v>7</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="24" t="s">
+      <c r="G13" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="H13" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I13" s="23"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="23"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="21"/>
       <c r="L13" s="2"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="23"/>
-      <c r="AA13" s="23"/>
-      <c r="AB13" s="23"/>
-      <c r="AC13" s="26"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="21"/>
+      <c r="AA13" s="21"/>
+      <c r="AB13" s="21"/>
+      <c r="AC13" s="24"/>
     </row>
     <row r="14" spans="1:29">
-      <c r="A14" s="15"/>
-      <c r="B14" s="17">
+      <c r="A14" s="13"/>
+      <c r="B14" s="15">
         <v>8</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="23" t="s">
+      <c r="F14" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H14" s="23" t="s">
+      <c r="H14" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I14" s="23"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="23"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="21"/>
       <c r="L14" s="2"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="23"/>
-      <c r="AA14" s="23"/>
-      <c r="AB14" s="23"/>
-      <c r="AC14" s="26"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="24"/>
     </row>
     <row r="15" spans="1:29">
-      <c r="A15" s="15"/>
-      <c r="B15" s="17">
+      <c r="A15" s="13"/>
+      <c r="B15" s="15">
         <v>9</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="24" t="s">
+      <c r="G15" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="23" t="s">
+      <c r="H15" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I15" s="23"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="23"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="21"/>
       <c r="L15" s="2"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
-      <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="23"/>
-      <c r="Z15" s="23"/>
-      <c r="AA15" s="23"/>
-      <c r="AB15" s="23"/>
-      <c r="AC15" s="26"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
+      <c r="V15" s="21"/>
+      <c r="W15" s="21"/>
+      <c r="X15" s="21"/>
+      <c r="Y15" s="21"/>
+      <c r="Z15" s="21"/>
+      <c r="AA15" s="21"/>
+      <c r="AB15" s="21"/>
+      <c r="AC15" s="24"/>
     </row>
     <row r="16" spans="1:29">
-      <c r="A16" s="15"/>
-      <c r="B16" s="17">
+      <c r="A16" s="13"/>
+      <c r="B16" s="15">
         <v>10</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="23" t="s">
+      <c r="F16" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="G16" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="23" t="s">
+      <c r="H16" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I16" s="23"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="23"/>
-      <c r="W16" s="23"/>
-      <c r="X16" s="23"/>
-      <c r="Y16" s="23"/>
-      <c r="Z16" s="23"/>
-      <c r="AA16" s="23"/>
-      <c r="AB16" s="23"/>
-      <c r="AC16" s="26"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="21"/>
+      <c r="W16" s="21"/>
+      <c r="X16" s="21"/>
+      <c r="Y16" s="21"/>
+      <c r="Z16" s="21"/>
+      <c r="AA16" s="21"/>
+      <c r="AB16" s="21"/>
+      <c r="AC16" s="24"/>
     </row>
     <row r="17" spans="1:29">
-      <c r="A17" s="15"/>
-      <c r="B17" s="17">
+      <c r="A17" s="13"/>
+      <c r="B17" s="15">
         <v>11</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="23" t="s">
+      <c r="F17" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="24" t="s">
+      <c r="G17" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="23" t="s">
+      <c r="H17" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="23"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="23"/>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="23"/>
-      <c r="AA17" s="23"/>
-      <c r="AB17" s="23"/>
-      <c r="AC17" s="26"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="21"/>
+      <c r="V17" s="21"/>
+      <c r="W17" s="21"/>
+      <c r="Y17" s="21"/>
+      <c r="Z17" s="21"/>
+      <c r="AA17" s="21"/>
+      <c r="AB17" s="21"/>
+      <c r="AC17" s="24"/>
     </row>
     <row r="18" spans="1:29" ht="15" customHeight="1">
-      <c r="A18" s="15"/>
-      <c r="B18" s="17">
+      <c r="A18" s="13"/>
+      <c r="B18" s="15">
         <v>12</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="F18" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="H18" s="23" t="s">
+      <c r="H18" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="I18" s="23"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="23"/>
-      <c r="V18" s="23"/>
-      <c r="W18" s="23"/>
-      <c r="X18" s="23"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="23"/>
-      <c r="AA18" s="23"/>
-      <c r="AB18" s="23"/>
-      <c r="AC18" s="26"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="21"/>
+      <c r="V18" s="21"/>
+      <c r="W18" s="21"/>
+      <c r="X18" s="21"/>
+      <c r="Y18" s="21"/>
+      <c r="Z18" s="21"/>
+      <c r="AA18" s="21"/>
+      <c r="AB18" s="21"/>
+      <c r="AC18" s="24"/>
     </row>
     <row r="19" spans="1:29" ht="15" customHeight="1">
-      <c r="A19" s="15"/>
-      <c r="B19" s="17">
+      <c r="A19" s="13"/>
+      <c r="B19" s="15">
         <v>13</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G19" s="24" t="s">
+      <c r="G19" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="H19" s="23" t="s">
+      <c r="H19" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="I19" s="23"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="23"/>
-      <c r="V19" s="23"/>
-      <c r="W19" s="23"/>
-      <c r="X19" s="23"/>
-      <c r="Y19" s="23"/>
-      <c r="Z19" s="23"/>
-      <c r="AA19" s="23"/>
-      <c r="AB19" s="23"/>
-      <c r="AC19" s="26"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="21"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
+      <c r="U19" s="21"/>
+      <c r="V19" s="21"/>
+      <c r="W19" s="21"/>
+      <c r="X19" s="21"/>
+      <c r="Y19" s="21"/>
+      <c r="Z19" s="21"/>
+      <c r="AA19" s="21"/>
+      <c r="AB19" s="21"/>
+      <c r="AC19" s="24"/>
     </row>
     <row r="20" spans="1:29">
-      <c r="A20" s="15"/>
-      <c r="B20" s="17">
+      <c r="A20" s="13"/>
+      <c r="B20" s="15">
         <v>14</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="F20" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G20" s="24" t="s">
+      <c r="G20" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H20" s="23" t="s">
+      <c r="H20" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="I20" s="23"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="23"/>
-      <c r="R20" s="23"/>
-      <c r="S20" s="23"/>
-      <c r="T20" s="23"/>
-      <c r="U20" s="23"/>
-      <c r="V20" s="23"/>
-      <c r="W20" s="23"/>
-      <c r="X20" s="23"/>
-      <c r="Y20" s="23"/>
-      <c r="Z20" s="23"/>
-      <c r="AA20" s="23"/>
-      <c r="AB20" s="23"/>
-      <c r="AC20" s="26"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="21"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="21"/>
+      <c r="V20" s="21"/>
+      <c r="W20" s="21"/>
+      <c r="X20" s="21"/>
+      <c r="Y20" s="21"/>
+      <c r="Z20" s="21"/>
+      <c r="AA20" s="21"/>
+      <c r="AB20" s="21"/>
+      <c r="AC20" s="24"/>
     </row>
     <row r="21" spans="1:29">
-      <c r="A21" s="15"/>
-      <c r="B21" s="17">
+      <c r="A21" s="13"/>
+      <c r="B21" s="15">
         <v>15</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="23" t="s">
+      <c r="F21" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="G21" s="24" t="s">
+      <c r="G21" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H21" s="23" t="s">
+      <c r="H21" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="I21" s="23"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
-      <c r="V21" s="23"/>
-      <c r="W21" s="23"/>
-      <c r="X21" s="23"/>
-      <c r="Y21" s="23"/>
-      <c r="Z21" s="23"/>
-      <c r="AA21" s="23"/>
-      <c r="AB21" s="23"/>
-      <c r="AC21" s="26"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="21"/>
+      <c r="M21" s="21"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="21"/>
+      <c r="R21" s="21"/>
+      <c r="S21" s="21"/>
+      <c r="T21" s="21"/>
+      <c r="U21" s="21"/>
+      <c r="V21" s="21"/>
+      <c r="W21" s="21"/>
+      <c r="X21" s="21"/>
+      <c r="Y21" s="21"/>
+      <c r="Z21" s="21"/>
+      <c r="AA21" s="21"/>
+      <c r="AB21" s="21"/>
+      <c r="AC21" s="24"/>
     </row>
     <row r="22" spans="1:29">
-      <c r="A22" s="15"/>
-      <c r="B22" s="17">
+      <c r="A22" s="13"/>
+      <c r="B22" s="15">
         <v>16</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="23" t="s">
+      <c r="F22" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="G22" s="24" t="s">
+      <c r="G22" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H22" s="23" t="s">
+      <c r="H22" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I22" s="23"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
-      <c r="S22" s="23"/>
-      <c r="T22" s="23"/>
-      <c r="U22" s="23"/>
-      <c r="V22" s="23"/>
-      <c r="W22" s="23"/>
-      <c r="X22" s="23"/>
-      <c r="Y22" s="23"/>
-      <c r="Z22" s="23"/>
-      <c r="AA22" s="23"/>
-      <c r="AB22" s="23"/>
-      <c r="AC22" s="26"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="21"/>
+      <c r="S22" s="21"/>
+      <c r="T22" s="21"/>
+      <c r="U22" s="21"/>
+      <c r="V22" s="21"/>
+      <c r="W22" s="21"/>
+      <c r="X22" s="21"/>
+      <c r="Y22" s="21"/>
+      <c r="Z22" s="21"/>
+      <c r="AA22" s="21"/>
+      <c r="AB22" s="21"/>
+      <c r="AC22" s="24"/>
     </row>
     <row r="23" spans="1:29">
-      <c r="A23" s="15"/>
-      <c r="B23" s="17">
+      <c r="A23" s="13"/>
+      <c r="B23" s="15">
         <v>17</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="D23" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E23" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="G23" s="24" t="s">
+      <c r="G23" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H23" s="23" t="s">
+      <c r="H23" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I23" s="23"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
-      <c r="T23" s="23"/>
-      <c r="U23" s="23"/>
-      <c r="V23" s="23"/>
-      <c r="W23" s="23"/>
-      <c r="X23" s="23"/>
-      <c r="Y23" s="23"/>
-      <c r="Z23" s="23"/>
-      <c r="AA23" s="23"/>
-      <c r="AB23" s="23"/>
-      <c r="AC23" s="26"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="21"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="21"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="21"/>
+      <c r="T23" s="21"/>
+      <c r="U23" s="21"/>
+      <c r="V23" s="21"/>
+      <c r="W23" s="21"/>
+      <c r="X23" s="21"/>
+      <c r="Y23" s="21"/>
+      <c r="Z23" s="21"/>
+      <c r="AA23" s="21"/>
+      <c r="AB23" s="21"/>
+      <c r="AC23" s="24"/>
     </row>
     <row r="24" spans="1:29">
-      <c r="A24" s="15"/>
-      <c r="B24" s="17">
+      <c r="A24" s="13"/>
+      <c r="B24" s="15">
         <v>18</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F24" s="23" t="s">
+      <c r="F24" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="G24" s="24" t="s">
+      <c r="G24" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H24" s="23" t="s">
+      <c r="H24" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="23"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="23"/>
-      <c r="S24" s="23"/>
-      <c r="T24" s="23"/>
-      <c r="U24" s="23"/>
-      <c r="V24" s="23"/>
-      <c r="W24" s="23"/>
-      <c r="X24" s="23"/>
-      <c r="Y24" s="23"/>
-      <c r="Z24" s="23"/>
-      <c r="AA24" s="23"/>
-      <c r="AB24" s="23"/>
-      <c r="AC24" s="26"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="21"/>
+      <c r="T24" s="21"/>
+      <c r="U24" s="21"/>
+      <c r="V24" s="21"/>
+      <c r="W24" s="21"/>
+      <c r="X24" s="21"/>
+      <c r="Y24" s="21"/>
+      <c r="Z24" s="21"/>
+      <c r="AA24" s="21"/>
+      <c r="AB24" s="21"/>
+      <c r="AC24" s="24"/>
     </row>
     <row r="25" spans="1:29">
-      <c r="A25" s="15"/>
-      <c r="B25" s="17">
+      <c r="A25" s="13"/>
+      <c r="B25" s="15">
         <v>19</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="23" t="s">
+      <c r="D25" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="E25" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F25" s="23" t="s">
+      <c r="F25" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="G25" s="24" t="s">
+      <c r="G25" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H25" s="23" t="s">
+      <c r="H25" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I25" s="23"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
-      <c r="S25" s="23"/>
-      <c r="T25" s="23"/>
-      <c r="U25" s="23"/>
-      <c r="V25" s="23"/>
-      <c r="W25" s="23"/>
-      <c r="X25" s="23"/>
-      <c r="Y25" s="23"/>
-      <c r="Z25" s="23"/>
-      <c r="AA25" s="23"/>
-      <c r="AB25" s="23"/>
-      <c r="AC25" s="26"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
+      <c r="R25" s="21"/>
+      <c r="S25" s="21"/>
+      <c r="T25" s="21"/>
+      <c r="U25" s="21"/>
+      <c r="V25" s="21"/>
+      <c r="W25" s="21"/>
+      <c r="X25" s="21"/>
+      <c r="Y25" s="21"/>
+      <c r="Z25" s="21"/>
+      <c r="AA25" s="21"/>
+      <c r="AB25" s="21"/>
+      <c r="AC25" s="24"/>
     </row>
     <row r="26" spans="1:29">
-      <c r="A26" s="15"/>
-      <c r="B26" s="17">
+      <c r="A26" s="13"/>
+      <c r="B26" s="15">
         <v>20</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="23" t="s">
+      <c r="F26" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="24" t="s">
+      <c r="G26" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H26" s="23" t="s">
+      <c r="H26" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I26" s="23"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23"/>
-      <c r="O26" s="23"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="23"/>
-      <c r="S26" s="23"/>
-      <c r="T26" s="23"/>
-      <c r="U26" s="23"/>
-      <c r="V26" s="23"/>
-      <c r="W26" s="23"/>
-      <c r="X26" s="23"/>
-      <c r="Y26" s="23"/>
-      <c r="Z26" s="23"/>
-      <c r="AA26" s="23"/>
-      <c r="AB26" s="23"/>
-      <c r="AC26" s="26"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="21"/>
+      <c r="S26" s="21"/>
+      <c r="T26" s="21"/>
+      <c r="U26" s="21"/>
+      <c r="V26" s="21"/>
+      <c r="W26" s="21"/>
+      <c r="X26" s="21"/>
+      <c r="Y26" s="21"/>
+      <c r="Z26" s="21"/>
+      <c r="AA26" s="21"/>
+      <c r="AB26" s="21"/>
+      <c r="AC26" s="24"/>
     </row>
     <row r="27" spans="1:29">
-      <c r="A27" s="15"/>
-      <c r="B27" s="17">
+      <c r="A27" s="13"/>
+      <c r="B27" s="15">
         <v>21</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="23" t="s">
+      <c r="D27" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="23" t="s">
+      <c r="F27" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="24" t="s">
+      <c r="G27" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H27" s="23" t="s">
+      <c r="H27" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I27" s="23"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="23"/>
-      <c r="S27" s="23"/>
-      <c r="T27" s="23"/>
-      <c r="U27" s="23"/>
-      <c r="V27" s="23"/>
-      <c r="W27" s="23"/>
-      <c r="X27" s="23"/>
-      <c r="Y27" s="23"/>
-      <c r="Z27" s="23"/>
-      <c r="AA27" s="23"/>
-      <c r="AB27" s="23"/>
-      <c r="AC27" s="26"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="21"/>
+      <c r="S27" s="21"/>
+      <c r="T27" s="21"/>
+      <c r="U27" s="21"/>
+      <c r="V27" s="21"/>
+      <c r="W27" s="21"/>
+      <c r="X27" s="21"/>
+      <c r="Y27" s="21"/>
+      <c r="Z27" s="21"/>
+      <c r="AA27" s="21"/>
+      <c r="AB27" s="21"/>
+      <c r="AC27" s="24"/>
     </row>
     <row r="28" spans="1:29">
-      <c r="A28" s="15"/>
-      <c r="B28" s="17">
+      <c r="A28" s="13"/>
+      <c r="B28" s="15">
         <v>22</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F28" s="23" t="s">
+      <c r="F28" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="G28" s="24" t="s">
+      <c r="G28" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H28" s="23" t="s">
+      <c r="H28" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I28" s="23"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
-      <c r="T28" s="23"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="23"/>
-      <c r="W28" s="23"/>
-      <c r="X28" s="23"/>
-      <c r="Y28" s="23"/>
-      <c r="Z28" s="23"/>
-      <c r="AA28" s="23"/>
-      <c r="AB28" s="23"/>
-      <c r="AC28" s="26"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="21"/>
+      <c r="R28" s="21"/>
+      <c r="S28" s="21"/>
+      <c r="T28" s="21"/>
+      <c r="U28" s="21"/>
+      <c r="V28" s="21"/>
+      <c r="W28" s="21"/>
+      <c r="X28" s="21"/>
+      <c r="Y28" s="21"/>
+      <c r="Z28" s="21"/>
+      <c r="AA28" s="21"/>
+      <c r="AB28" s="21"/>
+      <c r="AC28" s="24"/>
     </row>
     <row r="29" spans="1:29" ht="17.25" thickBot="1">
-      <c r="A29" s="15"/>
-      <c r="B29" s="18">
+      <c r="A29" s="13"/>
+      <c r="B29" s="16">
         <v>23</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="D29" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="28" t="s">
+      <c r="E29" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="G29" s="29" t="s">
+      <c r="G29" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="H29" s="28" t="s">
+      <c r="H29" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="I29" s="28"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
-      <c r="U29" s="28"/>
-      <c r="V29" s="28"/>
-      <c r="W29" s="28"/>
-      <c r="X29" s="28"/>
-      <c r="Y29" s="28"/>
-      <c r="Z29" s="28"/>
-      <c r="AA29" s="28"/>
-      <c r="AB29" s="28"/>
-      <c r="AC29" s="31"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="26"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="26"/>
+      <c r="S29" s="26"/>
+      <c r="T29" s="26"/>
+      <c r="U29" s="26"/>
+      <c r="V29" s="26"/>
+      <c r="W29" s="26"/>
+      <c r="X29" s="26"/>
+      <c r="Y29" s="26"/>
+      <c r="Z29" s="26"/>
+      <c r="AA29" s="26"/>
+      <c r="AB29" s="26"/>
+      <c r="AC29" s="29"/>
     </row>
     <row r="30" spans="1:29">
-      <c r="A30" s="15"/>
+      <c r="A30" s="13"/>
       <c r="B30" s="2" t="str">
         <v/>
       </c>
@@ -2667,7 +2632,7 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="32"/>
+      <c r="G30" s="30"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -2692,7 +2657,7 @@
       <c r="AC30" s="2"/>
     </row>
     <row r="31" spans="1:29">
-      <c r="A31" s="15"/>
+      <c r="A31" s="13"/>
       <c r="B31" s="2" t="str">
         <v/>
       </c>
@@ -2700,7 +2665,7 @@
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="32"/>
+      <c r="G31" s="30"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -3026,13 +2991,12 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="AC4:AC5"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="Y4:Y5"/>
-    <mergeCell ref="Z4:Z5"/>
-    <mergeCell ref="AA4:AA5"/>
-    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="V4:V5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
@@ -3045,15 +3009,16 @@
     <mergeCell ref="S4:S5"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="AC4:AC5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="Y4:Y5"/>
+    <mergeCell ref="Z4:Z5"/>
+    <mergeCell ref="AA4:AA5"/>
+    <mergeCell ref="AB4:AB5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I13:K15 Q7:U22 Y16:AC17 M13:P15 V16:X16 T23:AC23 V17:W22 X18:AC22 Q23:R23 Q24:AC31 V7:AC15 I16:P31 I7:P12" xr:uid="{F09DA95C-8BA7-4403-9C86-8EB5C46C10B5}">
       <formula1>$AD$2:$AD$3</formula1>
     </dataValidation>
